--- a/output/2026-09-13_10_Croazia_Koprivnicko-krizevacka_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-13_10_Croazia_Koprivnicko-krizevacka_Utensilerie_e_Macchine_Utensili.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Esistenza confermata: punto vendita a Bjelovarska 30, Koprivnica, tra le sedi di COMET (altre sedi: Novi Marof, Ludbreg, Bjelovar). Rivenditore autorizzato Unior/Swatycomet e dealer Husqvarna. Email non trovata.</t>
+          <t>Esistenza confermata: punto vendita a Bjelovarska 30, Koprivnica, tra le sedi di COMET (altre sedi: Novi Marof, Ludbreg, Bjelovar). Rivenditore autorizzato Unior/Swatycomet e dealer Husqvarna. Email non trovata. [DUPLICATO — vedi anche: 2026-09-12_22_Croazia_Varazdinska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,6 @@
           <t>ALDA d.o.o.</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Koprivničko-križevačka - Koprivnica</t>
@@ -542,7 +541,6 @@
           <t>KARMAT d.o.o.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Koprivničko-križevačka - Koprivnica</t>
@@ -590,7 +588,6 @@
           <t>Utensilerie e Macchine Utensili - noleggio e vendita utensili e macchine</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Sito confermato attivo: 'Najam i prodaja alata i strojeva Peteranec Koprivnica'. Nessun telefono/email reperiti.</t>

--- a/output/2026-09-13_10_Croazia_Koprivnicko-krizevacka_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-13_10_Croazia_Koprivnicko-krizevacka_Utensilerie_e_Macchine_Utensili.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
